--- a/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno2/anno2_task4_overall_dial.xlsx
+++ b/phase2-sft-alignment/sft-model/sft-eval/human-eval/results/anno2/anno2_task4_overall_dial.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A1DB3B-47D3-4A4A-86F5-58EA902D0080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87EC8C10-1CD7-4047-8D22-F886560D2F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="38400" windowHeight="19500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20" yWindow="900" windowWidth="41080" windowHeight="25660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,46 +56,46 @@
     <t>COMMENTS</t>
   </si>
   <si>
-    <t>SFTANNO-000013-0004</t>
-  </si>
-  <si>
-    <t>I've never really thought about it, but I'm interested in exploring more.</t>
-  </si>
-  <si>
-    <t>That's great, there's so much to discover and appreciate! It's unfortunate that ballet is often overlooked and underappreciated in our culture, but I'm glad you're interested in exploring it more.Have you looked into any other ballets yet?</t>
-  </si>
-  <si>
-    <t>That's great! There are so many different stories and themes within ballet, you're sure to find something you like. It's unfortunate that ballet is often seen as elitist or only for a certain type of person, but it's really for everyone to enjoy.Have you considered looking up any ballet companies in your area?</t>
-  </si>
-  <si>
-    <t>That's great! There are so many unique and interesting ballets out there, you'll definitely find something that resonates with you. Although I do think some ballets can be overly pretentious and snobbish, there are so many beautiful and unique stories that are worth exploring.Would you like some recommendations on where to start?</t>
-  </si>
-  <si>
-    <t>That's great, I'm sure you'll find something you love! Although there are so many beautiful ballets out there, it's unfortunate that the industry can be so limiting and exclusive.Have you ever seen a modern ballet?</t>
-  </si>
-  <si>
-    <t>That's great to hear, I think you'll find a lot of interesting stories and themes in ballet. It's a shame that there's still a lot of stigma and misconceptions surrounding ballet, but I hope you find some beautiful performances that change your mind.Do you have any questions about ballet or the performances you're planning to see?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000182-0004</t>
-  </si>
-  <si>
-    <t>The Holocaust, because I want to understand how such devastation could happen.</t>
-  </si>
-  <si>
-    <t>It's important to learn about history to prevent such tragedies from happening again. It's a heavy topic, but understanding history is crucial for a better future.Have you read any books about the Holocaust?</t>
-  </si>
-  <si>
-    <t>It's important to study history to prevent it from repeating itself. Yes, understanding the past can help us avoid making the same mistakes in the future.Have you ever visited any historical landmarks or sites?</t>
-  </si>
-  <si>
-    <t>It's important to remember and learn from history, especially the sad and difficult parts. I agree, it's crucial to learn from history and its darker aspects.Do you think history education should be more comprehensive?</t>
-  </si>
-  <si>
-    <t>It's important to learn about the past to prevent such events from happening again. It's a difficult subject, but important to understand.Have you read any books on the Holocaust that you would recommend?</t>
-  </si>
-  <si>
-    <t>I'm sorry to hear that. It's a difficult but important period of history to learn about.Have you read any good books about the Holocaust?</t>
+    <t>SFTANNO-000132-0004</t>
+  </si>
+  <si>
+    <t>I'm considering an adventure trip to Patagonia.</t>
+  </si>
+  <si>
+    <t>That sounds like an amazing experience! Patagonia's natural wonders are breathtaking. I'm surprised you're thinking of going there.Have you researched the logistics of the trip?</t>
+  </si>
+  <si>
+    <t>Patagonia sounds like an incredible adventure! That's a surprising and exciting choice! Patagonia offers breathtaking landscapes.Have you looked into tour operators for the trip?</t>
+  </si>
+  <si>
+    <t>That sounds like an incredible adventure! Patagonia is a dream destination for many, and I'm excited for you!Have you planned the details of your trip?</t>
+  </si>
+  <si>
+    <t>Patagonia is a breathtaking destination! It's awe-inspiring, but remember to prepare well for such an adventure.Have you started planning for the trip?</t>
+  </si>
+  <si>
+    <t>That's an exciting choice! Patagonia is a unique destination with breathtaking landscapes. I'm surprised you're going there!Have you started planning your Patagonia adventure?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000107-0004</t>
+  </si>
+  <si>
+    <t>It's so cloudy out, I don't even want to leave my house.</t>
+  </si>
+  <si>
+    <t>I hear you, sometimes it feels like there's no end in sight. Did you know that rain can actually be good for your mood? It's been proven to increase the production of serotonin in your brain.Do you have any favorite movies you like to watch on a rainy day?</t>
+  </si>
+  <si>
+    <t>I feel the same way, it's hard to be motivated when it's so gloomy. Have you tried going for a walk in the rain? It can be really refreshing!Do you have any upcoming plans for the weekend?</t>
+  </si>
+  <si>
+    <t>I get it, the clouds can be so depressing sometimes. I'm surprised you're feeling so down, you're usually so optimistic!Do you have any fun plans coming up?</t>
+  </si>
+  <si>
+    <t>I feel the same way, it's so hard to motivate myself when it's this dark outside. Have you ever tried going for a walk in the rain? It can be really peaceful.What's your favorite movie?</t>
+  </si>
+  <si>
+    <t>I know, it can be really discouraging to want to stay inside. Did you know that some people find cloudy days calming and peaceful?Have you tried any new restaurants lately?</t>
   </si>
   <si>
     <t>SFTANNO-000019-0004</t>
@@ -161,46 +161,46 @@
     <t>That's so sad to hear. It's like they don't care about the most vulnerable. It's heartbreaking to think about how many people will be affected by this.Do you think there's anything we can do to help those affected?</t>
   </si>
   <si>
-    <t>SFTANNO-000156-0004</t>
-  </si>
-  <si>
-    <t>There are! You can start with small changes, like rearranging furniture or adding plants to boost the energy in your space.</t>
-  </si>
-  <si>
-    <t>Wow, I had no idea! Thanks for the tips! I'm still a bit nervous about making changes, but I'm willing to try.What are some Feng Shui principles you follow in your own home?</t>
-  </si>
-  <si>
-    <t>That's a good idea. I never thought about the impact of plants on energy flow. But I'm still a bit afraid to make any changes. What if I mess up?Is there anything I can do to feel more confident about it?</t>
-  </si>
-  <si>
-    <t>I didn't think about that. Thanks for the tips! But I'm still a bit afraid of making too many changes at once.Do you have any other suggestions for making Feng Shui more manageable?</t>
-  </si>
-  <si>
-    <t>That's a great suggestion! I'll definitely have to give that a try. I'm just a bit nervous about messing up and not doing it right.Is there a way to avoid that?</t>
-  </si>
-  <si>
-    <t>That sounds doable. I never thought about incorporating plants into Feng Shui. But I'm worried about keeping plants alive. Do you have any tips?What kind of plants would you recommend for beginners?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000007-0004</t>
-  </si>
-  <si>
-    <t>They actually offered me the job!</t>
-  </si>
-  <si>
-    <t>Congratulations! That's fantastic news! Are you feeling overwhelmed by the new opportunity?Have you discussed your compensation package with the employer?</t>
-  </si>
-  <si>
-    <t>That's amazing news! Congratulations! Wow, congratulations! What are your initial thoughts about the new job?Have you thought about negotiating your salary or benefits?</t>
-  </si>
-  <si>
-    <t>That's great news! I'm happy for you, but now you have to think about the new job and the responsibilities that come with it.What are your thoughts on the job offer?</t>
-  </si>
-  <si>
-    <t>That's great news! Congratulations, but now comes the hard part: deciding if it's the right fit for you.Have you thought about negotiating your salary and benefits?</t>
-  </si>
-  <si>
-    <t>Congratulations! It's great news, but also scary, right?Have you started thinking about when you want to start?</t>
+    <t>SFTANNO-000094-0004</t>
+  </si>
+  <si>
+    <t>Actually, I always opt for middle seats. Fewer distractions around me.</t>
+  </si>
+  <si>
+    <t>I never thought about that before. I can't imagine sitting in the middle seat, it just sounds uncomfortable.Do you have any tips for avoiding jet lag?</t>
+  </si>
+  <si>
+    <t>Really? I can't imagine sitting in the middle seat. The middle seat is the worst; you're stuck in the middle of everything and can't even stretch out.Do you have any travel hacks or tips you like to use?</t>
+  </si>
+  <si>
+    <t>Really? I've never tried that before. That's interesting, but I'm not sure I could handle sitting in the middle with people on either side of me.Have you ever met someone interesting on a flight?</t>
+  </si>
+  <si>
+    <t>Really? I could never imagine choosing a middle seat. I can't believe you choose the middle seat. I would never want to be stuck in the middle.What's your favorite travel destination?</t>
+  </si>
+  <si>
+    <t>That's a unique choice! I'm surprised that you prefer middle seats; I always find them cramped and uncomfortable.Do you have any travel hacks or tips?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000103-0004</t>
+  </si>
+  <si>
+    <t>I've been browsing, but I don't want to compromise on quality either.</t>
+  </si>
+  <si>
+    <t>That's a tricky balance to find. It's tough when you can't find the right fit, but keep looking and don't settle for less.Do you have any favorite VR games or experiences?</t>
+  </si>
+  <si>
+    <t>It's important to find the right fit. It's a tough balance between finding something within budget and not sacrificing quality.Have you considered waiting for a sale or promotion on the VR headset you want?</t>
+  </si>
+  <si>
+    <t>That's a good point, you should only invest in something that meets your standards. It's important to prioritize quality, especially for something like a VR headset.Have you considered saving up or waiting for sales?</t>
+  </si>
+  <si>
+    <t>It's important to find the right balance between quality and price. It's tough to find the right balance, but I'm sure you'll find something that works for you.Have you considered waiting for a sale or discount?</t>
+  </si>
+  <si>
+    <t>It's important to find a balance between quality and affordability. It's tough when we want to invest in new technology, but have to be mindful of our budget.Have you considered any other alternatives or options?</t>
   </si>
   <si>
     <t>SFTANNO-000025-0004</t>
@@ -224,151 +224,151 @@
     <t>That's a great idea. I'm surprised at how much better you're feeling about the situation.Do you have any other concerns or questions?</t>
   </si>
   <si>
-    <t>SFTANNO-000167-0004</t>
-  </si>
-  <si>
-    <t>Do you think we'll see the implementation of AI in our daily lives soon?</t>
-  </si>
-  <si>
-    <t>It's hard to say, but I think we're already seeing it happen in many aspects of our lives. I'm happy to see that AI can help us in our daily lives, like in our homes or even in our cars.What do you think is the most exciting development in AI right now?</t>
-  </si>
-  <si>
-    <t>It's already happening in many ways, from smart homes to self-driving cars. I'm thrilled to think about the possibilities that AI could bring to our daily lives, making them easier and more efficient.What do you think will be the first significant change we'll see in our daily lives?</t>
-  </si>
-  <si>
-    <t>It's definitely a possibility, especially with how fast technology is advancing. I'm excited to see how AI will improve our daily lives and make things more efficient.What do you think will be the first area to see significant change?</t>
-  </si>
-  <si>
-    <t>It's already happening to some extent, but I think it will become more widespread in the coming years. It's exciting to think about the possibilities and advancements that AI will bring to our daily lives.What kind of AI implementation do you think will be the most beneficial to society?</t>
-  </si>
-  <si>
-    <t>It's possible, and it could make our lives easier in some ways. I'm excited to see how AI can help us streamline our daily routines and make things more efficient.Do you think there are any potential drawbacks?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000001-0004</t>
-  </si>
-  <si>
-    <t>I finished that book you recommended, and it was amazing!</t>
-  </si>
-  <si>
-    <t>I'm thrilled to hear that! I hope I don't jinx it, but I'm a bit nervous about recommending another book to you.What book was it and what did you enjoy about it?</t>
-  </si>
-  <si>
-    <t>I'm so glad you enjoyed it! I'm happy you liked it, but I'm a bit scared of not finding other books that you'll enjoy. What did you like about it?Do you have any other recommendations?</t>
-  </si>
-  <si>
-    <t>That's wonderful news! I'm so happy you enjoyed it! However, I'm a bit afraid that my other recommendations won't live up to that one.What's your next book on your list?</t>
-  </si>
-  <si>
-    <t>I'm so glad you enjoyed it! Now, what book should I recommend next? I'm afraid I'll disappoint you with my choice.Do you have any preferences or genres you're interested in?</t>
-  </si>
-  <si>
-    <t>That's fantastic news! I'm thrilled to hear that, but I hope I haven't spoiled anything for you.What was your favorite part of the book?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000004-0004</t>
-  </si>
-  <si>
-    <t>I'm worried about my son's eyesight. He's been complaining about headaches lately.</t>
-  </si>
-  <si>
-    <t>That's understandable. It's important to get it checked. Have you considered taking him for an eye exam?Maybe we can look up some local eye doctors together.</t>
-  </si>
-  <si>
-    <t>That's understandable. It's important to get it checked out. Maybe it's a good idea to schedule an appointment with an eye doctor.Have you considered taking him to an eye doctor for a checkup?</t>
-  </si>
-  <si>
-    <t>That's concerning. You should definitely take him to get his eyes checked. I'm sure it's just a precautionary measure, but it's always better to be safe than sorry.Have you noticed any other symptoms?</t>
-  </si>
-  <si>
-    <t>That sounds really concerning. Have you considered taking him to an optometrist to get his eyes checked?It's important to take care of our eyesight.</t>
-  </si>
-  <si>
-    <t>I can understand why you're concerned. It's important to have him checked by an eye doctor as soon as possible.Have you made an appointment for him yet?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000000-0004</t>
-  </si>
-  <si>
-    <t>You won't believe it! They killed off my favorite character, and I'm so mad about it!</t>
-  </si>
-  <si>
-    <t>That's so frustrating when that happens. That's understandable. How do you think the story will go on without them?Have you considered reading any other fantasy books in the meantime?</t>
-  </si>
-  <si>
-    <t>That's awful! I hate when that happens. I understand how you feel. How did you cope with that loss?Have you thought about what you want to read next?</t>
-  </si>
-  <si>
-    <t>I know how you feel. It's so infuriating when that happens. It's definitely a bummer when that happens. Have you considered skipping the next book?Have you tried talking to someone about it?</t>
-  </si>
-  <si>
-    <t>That's heartbreaking! I hate it when that happens. It's tough when a favorite character dies. How are you coping with it?Have you thought about rereading the series?</t>
-  </si>
-  <si>
-    <t>That's so frustrating! I'm sorry you had to experience that. It can be disappointing when a beloved character is taken away. How did you react?What's your favorite scene in the book?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000190-0004</t>
-  </si>
-  <si>
-    <t>I'm afraid I'm becoming addicted to binge-watching.</t>
-  </si>
-  <si>
-    <t>It's easy to get lost in a good series. It's great to lose yourself in a good show. Have you discovered any new favorites lately?How do you balance your TV watching with other activities?</t>
-  </si>
-  <si>
-    <t>Binge-watching can be a slippery slope. But at the same time, it's a great way to escape reality for a while.Have you tried setting limits for yourself?</t>
-  </si>
-  <si>
-    <t>It's easy to get sucked into a show, but remember to take breaks. I understand your fear, but you've discovered some great shows!Have you tried setting limits for yourself?</t>
-  </si>
-  <si>
-    <t>It's easy to get sucked into the binge-watching vortex. Don't worry; it happens to the best of us. How do you usually manage your time when binge-watching?Have you tried setting a daily limit for watching?</t>
-  </si>
-  <si>
-    <t>It's easy to get caught up in binge-watching. How are you managing your screen time? It's great that you're aware of it. Maybe you can try setting limits or taking breaks.Have you tried any TV shows that are less time-consuming?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000161-0004</t>
-  </si>
-  <si>
-    <t>Honestly, I just can't believe the company would put us through this unnecessary anxiety and tension.</t>
-  </si>
-  <si>
-    <t>It's outrageous. They should have handled the situation with more care and consideration. It's unacceptable. They need to be held accountable for their actions and be more transparent with their employees.Have you considered talking to any coworkers about taking action?</t>
-  </si>
-  <si>
-    <t>I know, it's completely unacceptable. They should be held accountable for the way they handled this situation. It's completely unprofessional.Have you considered talking to HR about your concerns?</t>
-  </si>
-  <si>
-    <t>It's unacceptable how they handled the situation. They should have been more transparent and considerate of their employees' feelings. It's infuriating how they handled this. They should have been more open and considerate of their employees' feelings.Do you think it's worth talking to HR about the handling of this situation?</t>
-  </si>
-  <si>
-    <t>I completely agree. It's unacceptable how they're handling this situation. It's infuriating that they would treat their employees like this. We deserve better than this.Have you considered reaching out to any other companies or exploring new job opportunities?</t>
-  </si>
-  <si>
-    <t>I completely agree. It's unacceptable that they would do this to their employees. I'm angry that they would treat their employees this way. They should be held accountable for their actions.Have you considered talking to HR about your concerns?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000003-0004</t>
-  </si>
-  <si>
-    <t>I have, but the thought of using someone else's lens disgusts me a little.</t>
-  </si>
-  <si>
-    <t>I can understand that, it's important to have your own equipment. I'm surprised that you've been using the same lens for so long, that's impressive!Do you have any recommendations for other lenses that I could try?</t>
-  </si>
-  <si>
-    <t>I understand where you're coming from, it can be unhygienic to use someone else's equipment. It's surprising how much hygiene can matter when using someone else's equipment.Have you tried using a lens cleaning kit?</t>
-  </si>
-  <si>
-    <t>I can understand why you'd feel that way. It's a big investment. I'm surprised you wouldn't consider renting a lens, it can be a cost-effective way to try out different lenses.Have you considered trying out different lenses to find the one that suits your needs?</t>
-  </si>
-  <si>
-    <t>I understand, it's not the cleanest option. I'm surprised you'd consider using someone else's lens.Maybe you can look into buying a new lens?</t>
-  </si>
-  <si>
-    <t>I can understand why you'd feel that way. It's a common concern. I'm surprised you haven't tried renting a lens before.Have you looked into buying a used lens online?</t>
+    <t>SFTANNO-000064-0004</t>
+  </si>
+  <si>
+    <t>I think we should reach out to local organizations and get involved in promoting change.</t>
+  </si>
+  <si>
+    <t>That's a great idea, it's important to use our voices and make our presence known. It's unacceptable that these issues are still going unchecked. It's time for us to be proactive and show our advocates for our beliefs.What local organizations do you know of that are promoting change?</t>
+  </si>
+  <si>
+    <t>That's a great idea. We can work together to make a positive impact. It's unacceptable that we still have to fight for basic rights and equality. It's time to take action and create change.What local organizations do you recommend we reach out to?</t>
+  </si>
+  <si>
+    <t>That's a great idea, it's important to support local initiatives. It's unacceptable that some people still see certain issues as acceptable. We need to keep pushing for change until we get the results we want.What local organizations do you think we should start with?</t>
+  </si>
+  <si>
+    <t>That's a great idea, we can work together to create a positive impact. It's frustrating that certain issues still persist, but we can work together to create change and make a difference.What organizations do you suggest we reach out to?</t>
+  </si>
+  <si>
+    <t>That's a great idea. We can also use social media to spread awareness and encourage others to take action. It's unacceptable that certain issues are still being overlooked and not given the attention they deserve. We need to be more vocal and take action to create change.How do you suggest we use social media to spread awareness?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000145-0004</t>
+  </si>
+  <si>
+    <t>That's a great idea! I hadn't thought about that.</t>
+  </si>
+  <si>
+    <t>I'm so glad I could help! Let's make a difference together. Yes, let's work together to make a positive impact on our planet!Do you have any other ideas for making sustainable changes?</t>
+  </si>
+  <si>
+    <t>I'm glad I could help! Every little bit helps! That's the spirit! Keep up the great work and we can make a difference together.What other sustainability changes are you thinking about making?</t>
+  </si>
+  <si>
+    <t>It's a great way to learn from others and get support. I'm so happy to hear that! It's so important to find resources and support for making these changes.What other changes do you want to make in your daily life?</t>
+  </si>
+  <si>
+    <t>I'm glad I could help! There are so many ways to get involved and make a difference. It's so inspiring to see people taking action and making a positive impact. Keep up the great work!Do you have any other sustainability tips or ideas you'd like to share?</t>
+  </si>
+  <si>
+    <t>It's always good to have a support system when making changes towards sustainability. It's great to see you taking steps towards sustainability! I'm excited to see what changes you'll make next.Have you considered supporting sustainable fashion brands?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000152-0004</t>
+  </si>
+  <si>
+    <t>I'm worried I won't be able to make anything as beautiful as the examples I've seen.</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but don't worry, it takes practice. It's frustrating that the scrapbooking industry can be so competitive and cutthroat.Have you considered taking a class to get some hands-on experience?</t>
+  </si>
+  <si>
+    <t>I understand, but remember that everyone starts somewhere. It's ridiculous that some people expect perfection right away.What kind of project are you thinking about making?</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but it's important to remember that it's about the memories, not the aesthetic. It's frustrating that the industry can make it seem like only perfection is acceptable.Have you thought about starting with a simple design and building from there?</t>
+  </si>
+  <si>
+    <t>It's normal to feel that way, but you'll get the hang of it. It's ridiculous that people can be so judgmental and critical.Have you thought about taking a class to learn some techniques?</t>
+  </si>
+  <si>
+    <t>I understand how you feel, but remember, it's all about practice. It's infuriating how much pressure society puts on people to create perfect crafts.What kind of scrapbooking materials do you like to use?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000159-0004</t>
+  </si>
+  <si>
+    <t>We should start by setting some ground rules for respectful discussion.</t>
+  </si>
+  <si>
+    <t>That's a great idea, we can work on that. I'm happy we're taking this step towards better communication.How do we create these rules?</t>
+  </si>
+  <si>
+    <t>Agreed, we need boundaries to prevent future conflicts. I'm happy we can start fresh with clear boundaries.How can we ensure we follow these rules?</t>
+  </si>
+  <si>
+    <t>Agreed, we need to establish boundaries. I'm happy we're taking steps towards a healthier conversation.What rules do you suggest?</t>
+  </si>
+  <si>
+    <t>I agree, we need to show each other respect. I'm happy we're taking steps towards a better conversation.What rules do you suggest we implement?</t>
+  </si>
+  <si>
+    <t>Agreed, let's make sure we listen and respect each other's opinions. I'm happy we're working towards a healthier conversation.What other steps can we take?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000096-0004</t>
+  </si>
+  <si>
+    <t>I missed the last train, and I'm stuck in the city.</t>
+  </si>
+  <si>
+    <t>Oh no, that's really inconvenient. I'm sorry you're stuck here alone. Do you need help getting a ride or anything?Is there anything I can do to help you?</t>
+  </si>
+  <si>
+    <t>Oh no, that's a scary situation. I'm sorry you're in that position. Is there a hotel nearby that you could stay at for the night?I'll help you find one if you need it.</t>
+  </si>
+  <si>
+    <t>Oh no, that's awful. Are you okay? I'm so sorry, it's a terrible feeling being stranded like that.Do you need help finding a nearby hotel or shelter?</t>
+  </si>
+  <si>
+    <t>That's really scary, especially in an unfamiliar place. It's tough to be in that situation, but we can help you find a safe place to stay.Do you have any friends or contacts in the area?</t>
+  </si>
+  <si>
+    <t>That's scary, are you okay? It's tough when things like this happen, but we'll figure it out.Can I help you find a taxi or other transportation option?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000089-0004</t>
+  </si>
+  <si>
+    <t>They have a really solid defense and excellent ball control.</t>
+  </si>
+  <si>
+    <t>Yeah, but they can be quite predictable at times. It's too bad when a team's strengths can also be their downfall.Do you have a favorite soccer player?</t>
+  </si>
+  <si>
+    <t>Yeah, they're hard to beat. It's too bad that not everyone has the same opportunities to play or even watch soccer.Do you have any upcoming soccer games you're looking forward to?</t>
+  </si>
+  <si>
+    <t>It's impressive to see a team that good. It's hard to watch a team like that and not feel sad about your own team's performance.Do you have any other teams you like to watch?</t>
+  </si>
+  <si>
+    <t>I agree, but sometimes their offense can be too predictable. It's too bad that some teams can't seem to compete with them, it's not very exciting.Who do you think is the best player on FC Barcelona?</t>
+  </si>
+  <si>
+    <t>Yeah, they're really good. It's a shame they don't have as much support as other teams, they deserve more recognition.Have you ever been to a live soccer game?</t>
+  </si>
+  <si>
+    <t>SFTANNO-000135-0004</t>
+  </si>
+  <si>
+    <t>I did a river rafting trip once, but the water was so dirty.</t>
+  </si>
+  <si>
+    <t>I can understand why that would be unpleasant. River rafting can be a thrilling adventure, but make sure you choose a reputable company and do your research beforehand.Have you tried any other outdoor adventures?</t>
+  </si>
+  <si>
+    <t>That sounds awful, I hate the idea of rafting in dirty water. It's important to prioritize safety and cleanliness when it comes to adventure activities.Have you ever tried whitewater rafting in a clean river?</t>
+  </si>
+  <si>
+    <t>That's not ideal, but there are plenty of other adventures to choose from. I can understand why you wouldn't want to raft in dirty water.Have you ever tried any adventure sports that involve water?</t>
+  </si>
+  <si>
+    <t>That sounds awful, I couldn't imagine rafting in dirty water. It's important to do your research and choose a reputable company that takes safety and cleanliness seriously.Have you gone rafting on a cleaner river since then?</t>
+  </si>
+  <si>
+    <t>That sounds gross. It's important to do research on the cleanliness of the river and the safety of the rafting company.Have you ever gone on a clean and safe river rafting trip?</t>
   </si>
   <si>
     <t>SFTANNO-000018-0004</t>
@@ -392,46 +392,46 @@
     <t>It is incredible, isn't it? Yes, it's fascinating how much we're learning about the universe. It's so exciting!Have you ever thought about studying astronomy?</t>
   </si>
   <si>
-    <t>SFTANNO-000002-0004</t>
-  </si>
-  <si>
-    <t>Not yet, everything is still uncertain due to the pandemic.</t>
-  </si>
-  <si>
-    <t>I understand, it's been tough for the industry. It's frustrating that the pandemic has caused so much uncertainty and loss in the industry.How do you stay motivated during these tough times?</t>
-  </si>
-  <si>
-    <t>That's understandable. It's been tough for everyone in the industry. It's frustrating how the pandemic has affected so many aspects of our lives, especially for those in creative fields.Do you have any other projects in mind?</t>
-  </si>
-  <si>
-    <t>I completely understand. It's tough to plan anything with so much uncertainty. It's frustrating how much the pandemic has disrupted the book industry and author events.Have you considered virtual events or book clubs?</t>
-  </si>
-  <si>
-    <t>That's understandable. The pandemic has affected everyone in different ways. It's frustrating that the pandemic is still affecting so many aspects of our lives. I hope things get better soon.When do you plan to release your book?</t>
-  </si>
-  <si>
-    <t>That's too bad, but it's understandable. Safety should always come first. It's frustrating that the pandemic is still affecting the industry. But I'm sure your book will still find its way to readers.Have you considered virtual events or book readings?</t>
-  </si>
-  <si>
-    <t>SFTANNO-000172-0004</t>
-  </si>
-  <si>
-    <t>I've tried to explain, but it's disheartening when they don't even want to listen.</t>
-  </si>
-  <si>
-    <t>It's infuriating when people refuse to listen. I'm surprised by their lack of openness. Have you considered sharing resources with them?How do you cope with their disbelief?</t>
-  </si>
-  <si>
-    <t>It's frustrating when people are unwilling to open their minds. It's surprising how resistant some can be to new ideas. How do you approach those who dismiss mindfulness?Do you think there's a way to change their perspective?</t>
-  </si>
-  <si>
-    <t>It's frustrating when people won't listen to your experiences. It's surprising how little some people are willing to listen. Have you considered sharing your experiences on social media?Would you like me to help you write a post about mindfulness?</t>
-  </si>
-  <si>
-    <t>It's infuriating when people refuse to consider other perspectives. It's surprising that they don't want to explore the benefits. How do you cope with their skepticism?Have you found other mindfulness enthusiasts to share your experiences with?</t>
-  </si>
-  <si>
-    <t>It's tough when people refuse to be open-minded. It's surprising how difficult it can be to change someone's perspective.Have you considered finding like-minded individuals to discuss mindfulness with?</t>
+    <t>SFTANNO-000163-0004</t>
+  </si>
+  <si>
+    <t>I wish I could go back in time to see history up close.</t>
+  </si>
+  <si>
+    <t>It's sad that we can't go back and witness history firsthand. It's a common feeling, but we should be grateful for the ability to learn about history through books and documentaries.What historical event would you like to witness if you could?</t>
+  </si>
+  <si>
+    <t>I understand the desire to experience history firsthand. While I understand your longing, it's essential to remember that time travel is just a fantasy.Have you ever visited any historical sites?</t>
+  </si>
+  <si>
+    <t>I understand your sentiment, but it's important to respect the timeline. We can learn a lot about history through books and documentaries.Have you ever read a book about a historical event?</t>
+  </si>
+  <si>
+    <t>It's a bittersweet feeling, wanting to experience history firsthand. We can always learn about history through research and study.It's important to appreciate history as it is, not just wish we could change it.</t>
+  </si>
+  <si>
+    <t>I know what you mean, it would be amazing to witness some of the most important events in history. Maybe there's a way to experience history without time travel, like visiting museums or historical sites.It's always important to appreciate and learn from the past.</t>
+  </si>
+  <si>
+    <t>SFTANNO-000102-0004</t>
+  </si>
+  <si>
+    <t>The new Pokemon game is such a cash grab. They're releasing the same version with only minor updates.</t>
+  </si>
+  <si>
+    <t>I can't believe they're taking advantage of their fans like that. It's infuriating, they should be focusing on making better games.Have you tried playing any other Pokemon games in the meantime?</t>
+  </si>
+  <si>
+    <t>I know, it's so frustrating. It feels like they're not even trying anymore.Have you tried playing any of the older Pokemon games?</t>
+  </si>
+  <si>
+    <t>I completely agree, it's a money-making scheme. They're exploiting their loyal fanbase, it's maddening.What other games have you been playing lately?</t>
+  </si>
+  <si>
+    <t>I completely understand your frustration. It's frustrating when companies rely on their brand instead of innovation.Have you considered trying a different game instead?</t>
+  </si>
+  <si>
+    <t>It's so frustrating when they do that. It's just a ploy to make more money, it's not fair to the fans.What other Pokemon games have you played?</t>
   </si>
   <si>
     <t>SFTANNO-000011-0004</t>
@@ -476,25 +476,25 @@
     <t>It's such a difficult balance. It's not fair that we have to worry about the cost of something that should be about celebrating love.Have you considered borrowing a dress from a friend or family member?</t>
   </si>
   <si>
-    <t>SFTANNO-000176-0004</t>
-  </si>
-  <si>
-    <t>No, just a pot for the pasta and a pan for the sauce.</t>
-  </si>
-  <si>
-    <t>Perfect, I have everything I need. Great, I'm ready to give it a try.When should I start?</t>
-  </si>
-  <si>
-    <t>Perfect, sounds easy enough. Let me know how it turns out! I'm happy to help if you need any guidance.Have you tried any other easy recipes lately?</t>
-  </si>
-  <si>
-    <t>Sounds easy, let's get started! Let's begin by boiling the pasta, and then we can make the sauce.How long do you think it'll take to make?</t>
-  </si>
-  <si>
-    <t>That's great to hear, I don't have a lot of kitchen equipment. Sounds like a perfect recipe for a beginner. I'm excited to try it out.Thanks for sharing this recipe with me.</t>
-  </si>
-  <si>
-    <t>That's all you need! It's a simple and satisfying dish. Sounds like a great meal. I'm excited to hear how it turns out.Let me know if you need any more tips or help.</t>
+    <t>SFTANNO-000062-0004</t>
+  </si>
+  <si>
+    <t>I'm thrilled to see more young people engaging in politics.</t>
+  </si>
+  <si>
+    <t>It's inspiring! It's great to see new voices and ideas. How do you think young people can make a difference?Have you engaged with any youth activism groups?</t>
+  </si>
+  <si>
+    <t>It's a positive development. It's encouraging to see young voices being heard. How can we continue to engage more people?Have you considered organizing events or workshops to encourage political participation?</t>
+  </si>
+  <si>
+    <t>That's fantastic! It's great to see the younger generation taking an interest in politics.Have you been following any inspiring young politicians or activists?</t>
+  </si>
+  <si>
+    <t>It's a positive trend! Yes, it's inspiring to see a more youthful interest in politics.How do you think we can continue encouraging young people to stay engaged?</t>
+  </si>
+  <si>
+    <t>It's great to see their enthusiasm. Yes, it's inspiring to witness their dedication. How do you think they can make a difference?Have you considered mentoring or supporting young political activists?</t>
   </si>
 </sst>
 </file>
@@ -516,10 +516,12 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -557,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -565,7 +567,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -917,7 +924,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="176" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
@@ -928,18 +935,18 @@
         <v>15</v>
       </c>
       <c r="D2" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="3">
-        <v>2</v>
+      <c r="F2" s="2">
+        <v>3</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="2">
         <v>3</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -951,11 +958,11 @@
       <c r="K2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="L2" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="112" x14ac:dyDescent="0.15">
+      <c r="L2" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="128" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -965,35 +972,35 @@
       <c r="C3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="3">
-        <v>5</v>
+      <c r="D3" s="2">
+        <v>4</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="3">
-        <v>5</v>
+      <c r="F3" s="2">
+        <v>3</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3">
-        <v>3</v>
+      <c r="H3" s="2">
+        <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="J3" s="3">
-        <v>5</v>
+      <c r="J3" s="2">
+        <v>3</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L3" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" ht="128" x14ac:dyDescent="0.15">
+      <c r="L3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="128" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1003,35 +1010,35 @@
       <c r="C4" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="3">
-        <v>4</v>
+      <c r="F4" s="2">
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="2">
         <v>4</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="J4" s="3">
+      <c r="J4" s="2">
         <v>3</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="L4" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="96" x14ac:dyDescent="0.15">
+      <c r="L4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1041,35 +1048,35 @@
       <c r="C5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="3">
+      <c r="F5" s="2">
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="2">
         <v>3</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J5" s="3">
-        <v>3</v>
+      <c r="J5" s="2">
+        <v>4</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="112" x14ac:dyDescent="0.15">
+      <c r="L5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -1079,35 +1086,35 @@
       <c r="C6" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>3</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="3">
-        <v>4</v>
+      <c r="F6" s="2">
+        <v>3</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H6" s="3">
-        <v>4</v>
+      <c r="H6" s="2">
+        <v>3</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="3">
+      <c r="J6" s="2">
         <v>4</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="112" x14ac:dyDescent="0.15">
+      <c r="L6" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
@@ -1117,35 +1124,35 @@
       <c r="C7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="3">
-        <v>4</v>
+      <c r="D7" s="2">
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F7" s="3">
-        <v>3</v>
+      <c r="F7" s="2">
+        <v>4</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H7" s="3">
-        <v>3</v>
+      <c r="H7" s="2">
+        <v>2</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="J7" s="3">
-        <v>4</v>
+      <c r="J7" s="2">
+        <v>2</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="L7" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="112" x14ac:dyDescent="0.15">
+      <c r="L7" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>55</v>
       </c>
@@ -1155,35 +1162,35 @@
       <c r="C8" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>3</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="3">
-        <v>1</v>
+      <c r="F8" s="2">
+        <v>3</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="H8" s="3">
-        <v>4</v>
+      <c r="H8" s="2">
+        <v>3</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="J8" s="3">
-        <v>4</v>
+      <c r="J8" s="2">
+        <v>3</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L8" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="112" x14ac:dyDescent="0.15">
+      <c r="L8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>62</v>
       </c>
@@ -1193,35 +1200,35 @@
       <c r="C9" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>4</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F9" s="3">
-        <v>5</v>
+      <c r="F9" s="2">
+        <v>3</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="2">
         <v>3</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J9" s="3">
-        <v>2</v>
+      <c r="J9" s="2">
+        <v>3</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="L9" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="144" x14ac:dyDescent="0.15">
+      <c r="L9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="176" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>69</v>
       </c>
@@ -1231,35 +1238,35 @@
       <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="3">
-        <v>4</v>
+      <c r="D10" s="2">
+        <v>3</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>3</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="2">
         <v>3</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="J10" s="3">
-        <v>4</v>
+      <c r="J10" s="2">
+        <v>3</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L10" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="96" x14ac:dyDescent="0.15">
+      <c r="L10" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="144" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>76</v>
       </c>
@@ -1269,35 +1276,35 @@
       <c r="C11" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>3</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F11" s="3">
-        <v>4</v>
+      <c r="F11" s="2">
+        <v>2</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="H11" s="3">
-        <v>4</v>
+      <c r="H11" s="2">
+        <v>3</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="3">
-        <v>4</v>
+      <c r="J11" s="2">
+        <v>3</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="L11" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="112" x14ac:dyDescent="0.15">
+      <c r="L11" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="144" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>83</v>
       </c>
@@ -1307,35 +1314,35 @@
       <c r="C12" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D12" s="3">
-        <v>5</v>
+      <c r="D12" s="2">
+        <v>3</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F12" s="3">
-        <v>4</v>
+      <c r="F12" s="2">
+        <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="H12" s="3">
-        <v>5</v>
+      <c r="H12" s="2">
+        <v>4</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="J12" s="3">
-        <v>3</v>
+      <c r="J12" s="2">
+        <v>4</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="L12" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="96" x14ac:dyDescent="0.15">
+      <c r="L12" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>90</v>
       </c>
@@ -1345,35 +1352,35 @@
       <c r="C13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>3</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F13" s="3">
-        <v>2</v>
+      <c r="F13" s="2">
+        <v>3</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="H13" s="3">
-        <v>2</v>
+      <c r="H13" s="2">
+        <v>3</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J13" s="3">
-        <v>4</v>
+      <c r="J13" s="2">
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="128" x14ac:dyDescent="0.15">
+      <c r="L13" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>97</v>
       </c>
@@ -1383,35 +1390,35 @@
       <c r="C14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D14" s="3">
-        <v>2</v>
+      <c r="D14" s="2">
+        <v>3</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="2">
         <v>4</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="2">
         <v>3</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="3">
-        <v>5</v>
+      <c r="J14" s="2">
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="L14" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="176" x14ac:dyDescent="0.15">
+      <c r="L14" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>104</v>
       </c>
@@ -1421,35 +1428,35 @@
       <c r="C15" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D15" s="3">
-        <v>5</v>
+      <c r="D15" s="2">
+        <v>3</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="2">
         <v>4</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15" s="2">
         <v>3</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="J15" s="3">
-        <v>5</v>
+      <c r="J15" s="2">
+        <v>2</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="128" x14ac:dyDescent="0.15">
+      <c r="L15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>111</v>
       </c>
@@ -1459,35 +1466,35 @@
       <c r="C16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="2">
         <v>4</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F16" s="3">
+      <c r="F16" s="2">
         <v>3</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16" s="2">
         <v>3</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="3">
-        <v>3</v>
+      <c r="J16" s="2">
+        <v>2</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="L16" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="112" x14ac:dyDescent="0.15">
+      <c r="L16" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="112" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>118</v>
       </c>
@@ -1497,35 +1504,35 @@
       <c r="C17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D17" s="3">
-        <v>1</v>
+      <c r="D17" s="2">
+        <v>4</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F17" s="3">
-        <v>1</v>
+      <c r="F17" s="2">
+        <v>3</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H17" s="3">
-        <v>4</v>
+      <c r="H17" s="2">
+        <v>3</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="J17" s="3">
-        <v>2</v>
+      <c r="J17" s="2">
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="128" x14ac:dyDescent="0.15">
+      <c r="L17" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="144" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>125</v>
       </c>
@@ -1535,35 +1542,35 @@
       <c r="C18" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="D18" s="3">
-        <v>5</v>
+      <c r="D18" s="2">
+        <v>3</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="F18" s="3">
-        <v>5</v>
+      <c r="F18" s="2">
+        <v>4</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H18" s="3">
-        <v>5</v>
+      <c r="H18" s="2">
+        <v>3</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="J18" s="3">
-        <v>5</v>
+      <c r="J18" s="2">
+        <v>4</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="L18" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="144" x14ac:dyDescent="0.15">
+      <c r="L18" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="112" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>132</v>
       </c>
@@ -1573,35 +1580,35 @@
       <c r="C19" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D19" s="3">
-        <v>5</v>
+      <c r="D19" s="2">
+        <v>3</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F19" s="3">
-        <v>3</v>
+      <c r="F19" s="2">
+        <v>2</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="H19" s="3">
-        <v>2</v>
+      <c r="H19" s="2">
+        <v>3</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="J19" s="3">
+      <c r="J19" s="2">
         <v>3</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="L19" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="128" x14ac:dyDescent="0.15">
+      <c r="L19" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="128" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>139</v>
       </c>
@@ -1611,35 +1618,35 @@
       <c r="C20" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D20" s="3">
-        <v>5</v>
+      <c r="D20" s="2">
+        <v>4</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="3">
-        <v>3</v>
+      <c r="F20" s="2">
+        <v>2</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H20" s="3">
-        <v>5</v>
+      <c r="H20" s="2">
+        <v>2</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="3">
-        <v>4</v>
+      <c r="J20" s="2">
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="L20" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="128" x14ac:dyDescent="0.15">
+      <c r="L20" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="128" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>146</v>
       </c>
@@ -1649,35 +1656,35 @@
       <c r="C21" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D21" s="3">
+      <c r="D21" s="2">
         <v>4</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="3">
-        <v>5</v>
+      <c r="F21" s="2">
+        <v>2</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H21" s="3">
-        <v>4</v>
+      <c r="H21" s="2">
+        <v>3</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="J21" s="3">
-        <v>5</v>
+      <c r="J21" s="2">
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L21" s="3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="80" x14ac:dyDescent="0.15">
+      <c r="L21" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="112" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>153</v>
       </c>
@@ -1687,35 +1694,40 @@
       <c r="C22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="3">
-        <v>1</v>
+      <c r="D22" s="2">
+        <v>3</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="2">
         <v>4</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="H22" s="3">
-        <v>4</v>
+      <c r="H22" s="2">
+        <v>3</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="J22" s="3">
-        <v>4</v>
+      <c r="J22" s="2">
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="L22" s="3">
-        <v>4</v>
+      <c r="L22" s="2">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D22 F2:F22 H2:H22 J2:J22 L2:L22" xr:uid="{35EB2117-EE87-419E-8A42-58C31378F635}">
+      <formula1>"1,2,3,4,5"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>